--- a/resources/data-imports/World Gems/map-gems.xlsx
+++ b/resources/data-imports/World Gems/map-gems.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AJ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelRow="0"/>
   <sheetData>
     <row r="1">
@@ -592,6 +592,11 @@
           <t>monster_atonement_range</t>
         </is>
       </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>gem_world_name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
@@ -611,47 +616,47 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.08-0.15</t>
+          <t>0.008-0.015</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.08-0.15</t>
+          <t>0.008-0.015</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.08-0.15</t>
+          <t>0.008-0.015</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.08-0.15</t>
+          <t>0.008-0.015</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.08-0.15</t>
+          <t>0.008-0.015</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.08-0.15</t>
+          <t>0.008-0.015</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.08-0.15</t>
+          <t>0.008-0.015</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.08-0.15</t>
+          <t>0.008-0.015</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.08-0.15</t>
+          <t>0.008-0.015</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -665,62 +670,67 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.04-0.12</t>
+          <t>0.004-0.012</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.06-0.12</t>
+          <t>0.006-0.012</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.06-0.12</t>
+          <t>0.006-0.012</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.06-0.12</t>
+          <t>0.006-0.012</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.06-0.12</t>
+          <t>0.006-0.012</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.06-0.12</t>
+          <t>0.006-0.012</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.06-0.12</t>
+          <t>0.006-0.012</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.06-0.12</t>
+          <t>0.006-0.012</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.06-0.12</t>
+          <t>0.006-0.012</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.06-0.12</t>
+          <t>0.006-0.012</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.06-0.12</t>
+          <t>0.006-0.012</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.06-0.12</t>
+          <t>0.006-0.012</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Duskfall Requiem</t>
         </is>
       </c>
     </row>
@@ -742,47 +752,47 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.12-0.2</t>
+          <t>0.012-0.02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.12-0.2</t>
+          <t>0.012-0.02</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.12-0.2</t>
+          <t>0.012-0.02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.12-0.2</t>
+          <t>0.012-0.02</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.12-0.2</t>
+          <t>0.012-0.02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.12-0.2</t>
+          <t>0.012-0.02</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.12-0.2</t>
+          <t>0.012-0.02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.12-0.2</t>
+          <t>0.012-0.02</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.12-0.2</t>
+          <t>0.012-0.02</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -796,62 +806,67 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.2-0.3</t>
+          <t>0.02-0.03</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.18-0.25</t>
+          <t>0.018-0.025</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.18-0.25</t>
+          <t>0.018-0.025</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.18-0.25</t>
+          <t>0.018-0.025</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.18-0.25</t>
+          <t>0.018-0.025</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.18-0.25</t>
+          <t>0.018-0.025</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.18-0.25</t>
+          <t>0.018-0.025</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.18-0.25</t>
+          <t>0.018-0.025</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.18-0.25</t>
+          <t>0.018-0.025</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.18-0.25</t>
+          <t>0.018-0.025</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.18-0.25</t>
+          <t>0.018-0.025</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.18-0.25</t>
+          <t>0.018-0.025</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Ember Choir of the Damned</t>
         </is>
       </c>
     </row>
@@ -873,47 +888,47 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -927,82 +942,87 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.28-0.39</t>
+          <t>0.028-0.039</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Between Two Silences</t>
         </is>
       </c>
     </row>
@@ -1024,47 +1044,47 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1078,82 +1098,87 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.42-0.48</t>
+          <t>0.042-0.048</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Echoes That Lied</t>
         </is>
       </c>
     </row>
@@ -1175,47 +1200,47 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.35-0.43</t>
+          <t>0.035-0.043</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1229,62 +1254,67 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.42-0.48</t>
+          <t>0.042-0.048</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.48-0.65</t>
+          <t>0.048-0.065</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>A Child's Splintered Mind</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1336,47 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.25-0.38</t>
+          <t>0.025-0.038</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1360,62 +1390,67 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.28-0.39</t>
+          <t>0.028-0.039</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.3-0.55</t>
+          <t>0.03-0.055</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Where Warmth Goes to Die</t>
         </is>
       </c>
     </row>
